--- a/survey_templates/048_skincare_questionnaire--survey_templates.xlsx
+++ b/survey_templates/048_skincare_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -2041,29 +2041,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>anti-aging</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Anti-aging</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>skincare_preferences_choices</t>
+          <t>skincare_frequency_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>a_few_times_a_week</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>A few times a week</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>a_few_times_a_week</t>
+          <t>once_a_week</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>A few times a week</t>
+          <t>Once a week</t>
         </is>
       </c>
     </row>
@@ -2109,29 +2109,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>once_a_week</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Once a week</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>skincare_frequency_choices</t>
+          <t>skincare_purchase_method_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>less_than_once_a_week</t>
+          <t>in-store</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Less than once a week</t>
+          <t>In-store</t>
         </is>
       </c>
     </row>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>in-store</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>In-store</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -2177,29 +2177,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>skincare_purchase_method_choices</t>
+          <t>skincare_product_satisfaction_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2262,29 +2262,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>skincare_product_satisfaction_choices</t>
+          <t>skincare_recommendation_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Very dissatisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2296,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2313,27 +2313,10 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>skincare_recommendation_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>not_sure</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
         <is>
           <t>Not sure</t>
         </is>
